--- a/education_forms/009_student_satisfaction_with_academic_services_evaluation_form--education_forms.xlsx
+++ b/education_forms/009_student_satisfaction_with_academic_services_evaluation_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>student_satisfaction_with_academic_services_evaluation_form_page_1</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Overall Experience</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,40 +538,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>student_satisfaction_page_2</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>Satisfaction with Quality of Instruction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is your overall satisfaction with the academic services provided?</t>
+          <t>Satisfaction with Availability of Resources</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,35 +589,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1_response</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Satisfaction with Support from Instructors</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Satisfaction with Support from Peers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_2_response</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Quality of Academic Advice and Guidance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_3_response</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Availability of Facilities</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>student_feedback</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Availability of Library and Other Resources</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,21 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Overall Satisfaction (2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>suggestions</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Suggestions and Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>feedback</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional Feedback</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
@@ -781,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_response_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -798,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_response_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -815,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_response_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -832,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_response_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_1_response_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -866,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_response_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,136 +929,663 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_response_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>availability_of_resources</t>
+          <t>availability_of_facilities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Availability of resources</t>
+          <t>Availability of facilities</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_response_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>support_from_instructors</t>
+          <t>availability_of_library_and_other_resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Support from instructors</t>
+          <t>Availability of library and other resources</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_2_response_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>support_from_peers</t>
+          <t>support_from_instructors</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Support from peers</t>
+          <t>Support from instructors</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_2_response_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>support_from_peers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Support from peers</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_3_response_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>quality_of_academic_advice_and_guidance</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Quality of academic advice and guidance</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_3_response_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>availability_of_facilities</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Availability of facilities</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_3_response_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>availability_of_library_and_other_resources</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Availability of library and other resources</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_3_response_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>neither</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Neither</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
